--- a/artfynd/A 11678-2024 artfynd.xlsx
+++ b/artfynd/A 11678-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>100894581</v>
       </c>
       <c r="B2" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493010.9945585373</v>
+        <v>493012</v>
       </c>
       <c r="R2" t="n">
-        <v>6562161.037314896</v>
+        <v>6562161</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,19 +755,9 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,12 +787,7 @@
         <v>100894585</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493010.9945585373</v>
+        <v>493012</v>
       </c>
       <c r="R3" t="n">
-        <v>6562161.037314896</v>
+        <v>6562161</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -876,19 +856,9 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
